--- a/downloads_generacion/extracted_ingresos_c_iny_0824.xlsx
+++ b/downloads_generacion/extracted_ingresos_c_iny_0824.xlsx
@@ -431,27 +431,27 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CENTRAL</t>
+          <t>AGENTE</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Energía KWh</t>
+          <t>Energía MWh</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Ingresos Energía USD</t>
+          <t>Ingresos Energía MWh</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Ingresos Renovables USD</t>
+          <t>Ingresos Renovables MWh</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Ingresos Potencia USD</t>
+          <t>Ingresos Potencia kW</t>
         </is>
       </c>
     </row>

--- a/downloads_generacion/extracted_ingresos_c_iny_0824.xlsx
+++ b/downloads_generacion/extracted_ingresos_c_iny_0824.xlsx
@@ -431,27 +431,27 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AGENTE</t>
+          <t>CENTRAL</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Energía MWh</t>
+          <t>Energía KWh</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Ingresos Energía MWh</t>
+          <t>Ingresos Energía USD</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Ingresos Renovables MWh</t>
+          <t>Ingresos Renovables USD</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Ingresos Potencia kW</t>
+          <t>Ingresos Potencia USD</t>
         </is>
       </c>
     </row>
